--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104533_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104533_W9.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7793</v>
+        <v>2.9118</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3783</v>
+        <v>0.2807</v>
       </c>
       <c r="F2" t="n">
-        <v>2.401</v>
+        <v>2.631</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1004</v>
+        <v>-2.1124</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.5322</v>
+        <v>-2.5413</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4318</v>
+        <v>0.4289</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.308</v>
+        <v>-1.3527</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8148</v>
+        <v>-0.8456</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7924</v>
+        <v>-0.7598</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7175</v>
+        <v>-1.6957</v>
       </c>
       <c r="O2" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3218</v>
+        <v>-0.5111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6896</v>
+        <v>-0.328</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3678</v>
+        <v>-0.183</v>
       </c>
       <c r="V2" t="n">
-        <v>5.7848</v>
+        <v>5.7629</v>
       </c>
       <c r="W2" t="n">
-        <v>5.3992</v>
+        <v>5.3759</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5407</v>
+        <v>0.6591</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0286</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5693</v>
+        <v>1.5739</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0882</v>
+        <v>1.0272</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7923</v>
+        <v>2.559</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2959</v>
+        <v>-1.5318</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2499</v>
+        <v>2.3305</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2499</v>
+        <v>3.8955</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.5651</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1617</v>
+        <v>-1.3032</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4576</v>
+        <v>-1.3365</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.0333</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>3.4145</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0668</v>
+        <v>-0.3681</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2389</v>
+        <v>-0.9203</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3058</v>
+        <v>0.5521</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4822</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2708</v>
+        <v>0.226</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5397</v>
+        <v>-0.343</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8104</v>
+        <v>0.569</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0363</v>
+        <v>1.0888</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5583</v>
+        <v>0.7845</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5221</v>
+        <v>0.3043</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3701</v>
+        <v>1.2303</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9136</v>
+        <v>1.2303</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5435</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3338</v>
+        <v>-0.1416</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3552</v>
+        <v>-0.4458</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0214</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4025</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4025</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7655</v>
+        <v>-0.2497</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5999</v>
+        <v>-0.523</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8344</v>
+        <v>0.2733</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3232</v>
+        <v>-0.0175</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2087</v>
+        <v>-1.6375</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1145</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4318</v>
+        <v>-0.6679</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.6988</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4318</v>
+        <v>0.0309</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.4382</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.9825</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4318</v>
+        <v>-1.1061</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.6813</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4318</v>
+        <v>0.5752</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3451</v>
+        <v>-0.3496</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2087</v>
+        <v>-0.3441</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1364</v>
+        <v>-0.0055</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8518</v>
+        <v>-0.2187</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3313</v>
+        <v>-0.1394</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5205</v>
+        <v>-0.0793</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3703</v>
+        <v>-0.4289</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1544</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2159</v>
+        <v>-0.4289</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0346</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.405</v>
+        <v>-0.4289</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1891</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2159</v>
+        <v>-0.4289</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2547</v>
+        <v>-0.2451</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1155</v>
+        <v>-0.1057</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8532</v>
+        <v>-0.5997</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2212</v>
+        <v>0.5134</v>
       </c>
       <c r="F7" t="n">
-        <v>1.368</v>
+        <v>-1.1131</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6746</v>
+        <v>-0.3722</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7145</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0399</v>
+        <v>0.2311</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4565</v>
+        <v>1.3788</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9871</v>
+        <v>1.1926</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5306</v>
+        <v>0.1862</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1311</v>
+        <v>-1.751</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7016</v>
+        <v>-1.7959</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5705</v>
+        <v>0.0449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1786</v>
+        <v>-0.3461</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9557</v>
+        <v>-0.272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2229</v>
+        <v>-0.0741</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.7872</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0386</v>
+        <v>-0.3326</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0231</v>
+        <v>-0.4546</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3795</v>
+        <v>-0.3668</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6061</v>
+        <v>-0.1523</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2266</v>
+        <v>-0.2144</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3917</v>
+        <v>0.0345</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2051</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1866</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7711</v>
+        <v>-0.4012</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8112</v>
+        <v>-0.1868</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>-0.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4952</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7126</v>
+        <v>-0.1928</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.1394</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0526</v>
+        <v>-0.0534</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0363</v>
+        <v>-2.0218</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6431</v>
+        <v>-1.5846</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3932</v>
+        <v>-0.4372</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2674</v>
+        <v>-1.2675</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4011</v>
+        <v>-0.402</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8663</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9293</v>
+        <v>-0.9388</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3381</v>
+        <v>-0.3287</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7363</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4869</v>
+        <v>-0.4182</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2535</v>
+        <v>-0.3181</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1287</v>
+        <v>-2.1879</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1153</v>
+        <v>-1.9459</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0134</v>
+        <v>-0.242</v>
       </c>
       <c r="G10" t="n">
         <v>-3.288</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3665</v>
+        <v>0.3676</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6544</v>
+        <v>-3.6556</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8467</v>
+        <v>-1.8326</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1337</v>
+        <v>-0.1974</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6079</v>
+        <v>-0.4207</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4742</v>
+        <v>0.2232</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.749</v>
+        <v>-2.2216</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3612</v>
+        <v>-0.0851</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3878</v>
+        <v>-2.1365</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8418</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1646</v>
+        <v>0.1556</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6771</v>
+        <v>0.6856</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8643</v>
+        <v>1.8433</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0225</v>
+        <v>-1.0022</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4055</v>
+        <v>-0.8838</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0253</v>
+        <v>-0.7204</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3802</v>
+        <v>-0.1634</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2407</v>
+        <v>-2.9246</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8143</v>
+        <v>-0.582</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4263</v>
+        <v>-2.3426</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7699</v>
+        <v>-3.7769</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1256</v>
+        <v>-1.1204</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6443</v>
+        <v>-2.6565</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1812</v>
+        <v>-1.225</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1114</v>
+        <v>1.0924</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2926</v>
+        <v>-2.3175</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5887</v>
+        <v>-2.5519</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.237</v>
+        <v>-2.2128</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7806</v>
+        <v>-0.4727</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7258</v>
+        <v>-0.4465</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0548</v>
+        <v>-0.0262</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.576499999999999</v>
+        <v>-7.1821</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8465</v>
+        <v>-6.770799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7300999999999993</v>
+        <v>-0.4113999999999995</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.3156</v>
+        <v>-9.323400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6522</v>
+        <v>-1.6514</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.663499999999999</v>
+        <v>-7.671800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5073</v>
+        <v>2.283699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>9.691599999999999</v>
+        <v>9.557</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.1843</v>
+        <v>-7.273300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.8229</v>
+        <v>-11.6072</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.344</v>
+        <v>-11.2085</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4792</v>
+        <v>-0.3984999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6709</v>
+        <v>5.6909</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2809</v>
+        <v>19.3487</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.9281</v>
+        <v>-4.5527</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.063800000000001</v>
+        <v>-4.672000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1359000000000002</v>
+        <v>0.1192</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9960999999999995</v>
+        <v>1.0032</v>
       </c>
       <c r="W13" t="n">
-        <v>9.32</v>
+        <v>9.275399999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.324100000000001</v>
+        <v>-8.2723</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.76</v>
+        <v>4.537</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1059</v>
+        <v>3.0622</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6541</v>
+        <v>1.4748</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3231</v>
+        <v>1.3254</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2164</v>
+        <v>1.215</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1067</v>
+        <v>0.1104</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6728</v>
+        <v>2.6431</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9021</v>
+        <v>2.8818</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3497</v>
+        <v>-1.3177</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6857</v>
+        <v>-1.6668</v>
       </c>
       <c r="O14" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>1.159</v>
+        <v>0.9432</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0302</v>
+        <v>-0.0283</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1892</v>
+        <v>0.9715</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.868</v>
+        <v>3.3631</v>
       </c>
       <c r="E15" t="n">
-        <v>4.744</v>
+        <v>3.9785</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.876</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8077</v>
+        <v>2.7961</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1472</v>
+        <v>1.146</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6605</v>
+        <v>1.65</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1415</v>
+        <v>4.0993</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6597</v>
+        <v>2.6405</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4818</v>
+        <v>1.4588</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3338</v>
+        <v>-1.3032</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5125</v>
+        <v>-1.4945</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8296</v>
+        <v>0.3425</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5474</v>
+        <v>-0.1584</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2822</v>
+        <v>0.501</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1892</v>
+        <v>1.1758</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8772</v>
+        <v>3.3365</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1795</v>
+        <v>1.5875</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6977</v>
+        <v>1.749</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6456</v>
+        <v>1.8509</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3407</v>
+        <v>0.8441</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9862</v>
+        <v>1.0067</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0454</v>
+        <v>1.4621</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0693</v>
+        <v>1.4479</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1147</v>
+        <v>0.0142</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.3887</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4099</v>
+        <v>-0.6037</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1009</v>
+        <v>0.9925</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>1.485</v>
+        <v>0.8514</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2249</v>
+        <v>0.174</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2601</v>
+        <v>0.6774</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4997</v>
+        <v>2.7758</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0249</v>
+        <v>0.5881</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4748</v>
+        <v>2.1876</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8526</v>
+        <v>0.6526</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8397</v>
+        <v>-0.3336</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0129</v>
+        <v>0.9861</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4838</v>
+        <v>-0.0504</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4546</v>
+        <v>0.0689</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0292</v>
+        <v>-0.1194</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3688</v>
+        <v>0.703</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6149</v>
+        <v>-0.4025</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9837</v>
+        <v>1.1055</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.008200000000000001</v>
+        <v>1.3704</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4174</v>
+        <v>0.6385</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4255</v>
+        <v>0.7319</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1534</v>
+        <v>1.3532</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4798</v>
+        <v>0.431</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6736</v>
+        <v>0.9222</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6373</v>
+        <v>-0.4202</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1011</v>
+        <v>-1.7209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7383</v>
+        <v>1.3007</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3195</v>
+        <v>-0.5628</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6234</v>
+        <v>-0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3039</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3178</v>
+        <v>0.1426</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7245</v>
+        <v>-1.1209</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0423</v>
+        <v>1.2634</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>2.157</v>
+        <v>0.4564</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2945</v>
+        <v>-0.2047</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8626</v>
+        <v>0.6611</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4141</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4141</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9825</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5357</v>
+        <v>-0.0042</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5182</v>
+        <v>0.6377</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3044</v>
+        <v>0.6379</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3608</v>
+        <v>-0.0978</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9436</v>
+        <v>0.7358</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4243</v>
+        <v>0.3073</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4243</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.3132</v>
       </c>
       <c r="M19" t="n">
-        <v>0.88</v>
+        <v>0.3306</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0636</v>
+        <v>-0.7184</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9436</v>
+        <v>1.049</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9488</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7838</v>
+        <v>1.6283</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4386</v>
+        <v>0.8267</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3452</v>
+        <v>0.8016</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1568</v>
+        <v>-1.405</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.9961</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4604</v>
+        <v>0.3373</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0241</v>
+        <v>0.2503</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4845</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4348</v>
+        <v>4.3031</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7303</v>
+        <v>2.1281</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2955</v>
+        <v>2.1751</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5586</v>
+        <v>5.305</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5959</v>
+        <v>3.637</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>1.668</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1238</v>
+        <v>-1.0018</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1344</v>
+        <v>-1.5089</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2582</v>
+        <v>0.5071</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-5.6908</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4243</v>
+        <v>0.3787</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6775</v>
+        <v>-0.4533</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2531</v>
+        <v>0.832</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.24</v>
+        <v>0.2886</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7037</v>
+        <v>-1.6818</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4636</v>
+        <v>1.9704</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5499</v>
+        <v>3.303</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7445</v>
+        <v>2.3554</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1946</v>
+        <v>0.9476</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5181</v>
+        <v>2.4132</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5554</v>
+        <v>2.4132</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0318</v>
+        <v>0.8898</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1891</v>
+        <v>-0.0578</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1573</v>
+        <v>0.9476</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2365</v>
+        <v>1.1057</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2782</v>
+        <v>0.3227</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0417</v>
+        <v>0.7831</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>-1.1609</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>-1.0032</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5354</v>
+        <v>-0.1832</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2912</v>
+        <v>-0.7141</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2442</v>
+        <v>0.5309</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2952</v>
+        <v>-1.5537</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1254</v>
+        <v>-1.7489</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1698</v>
+        <v>0.1952</v>
       </c>
       <c r="J22" t="n">
-        <v>5.3304</v>
+        <v>-1.5248</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6538</v>
+        <v>-1.562</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6765</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0352</v>
+        <v>-0.0289</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5284</v>
+        <v>-0.1868</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4932</v>
+        <v>0.1579</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.6293</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.6708</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4942</v>
+        <v>-0.1743</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0434</v>
+        <v>-0.2788</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5492</v>
+        <v>0.1046</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3575</v>
+        <v>-3.2844</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5363</v>
+        <v>-3.2569</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1789</v>
+        <v>-0.0276</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4844</v>
+        <v>-2.0741</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2045</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2798</v>
+        <v>-1.1633</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6651</v>
+        <v>-1.7746</v>
       </c>
       <c r="K23" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.307</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6744</v>
+        <v>-1.4676</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8193</v>
+        <v>-0.2995</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2139</v>
+        <v>-0.6037</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3946</v>
+        <v>0.3043</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6052</v>
+        <v>-0.3485</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.378</v>
+        <v>-0.3441</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9832</v>
+        <v>-0.0044</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0246</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8919</v>
+        <v>-3.7915</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.713</v>
+        <v>-3.8293</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1789</v>
+        <v>0.0378</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.0812</v>
+        <v>-1.4975</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9164</v>
+        <v>-1.2252</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1648</v>
+        <v>-0.2723</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7623</v>
+        <v>-0.7101</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3015</v>
+        <v>-0.0322</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4608</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3189</v>
+        <v>-0.7874</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6149</v>
+        <v>-1.1931</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2959</v>
+        <v>0.4057</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9448</v>
+        <v>0.1824</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8166</v>
+        <v>-0.6137</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1282</v>
+        <v>0.7961</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-2.0212</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.576400000000001</v>
+        <v>9.366</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7300999999999993</v>
+        <v>0.4112999999999989</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8463</v>
+        <v>8.954300000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>9.3156</v>
+        <v>9.323499999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.652</v>
+        <v>1.651399999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>7.663500000000001</v>
+        <v>7.672000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>11.8228</v>
+        <v>11.6073</v>
       </c>
       <c r="K25" t="n">
-        <v>11.3437</v>
+        <v>11.2086</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4790000000000003</v>
+        <v>0.3985000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5073</v>
+        <v>-2.2838</v>
       </c>
       <c r="N25" t="n">
-        <v>-9.691800000000001</v>
+        <v>-9.557099999999998</v>
       </c>
       <c r="O25" t="n">
-        <v>7.184399999999999</v>
+        <v>7.2734</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.6709</v>
+        <v>-5.6909</v>
       </c>
       <c r="Q25" t="n">
-        <v>-19.2809</v>
+        <v>-19.3489</v>
       </c>
       <c r="R25" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S25" t="n">
-        <v>5.928</v>
+        <v>6.736200000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1359</v>
+        <v>-0.1194</v>
       </c>
       <c r="U25" t="n">
-        <v>6.0638</v>
+        <v>6.855899999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9959999999999998</v>
+        <v>-1.0031</v>
       </c>
       <c r="W25" t="n">
-        <v>8.3241</v>
+        <v>8.2723</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.32</v>
+        <v>-9.275500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104533_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104533_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.2723</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104533_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.275500000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
